--- a/AAII_Financials/Yearly/CMTV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CMTV_YR_FIN.xlsx
@@ -3074,7 +3074,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1127700</v>
+        <v>1128200</v>
       </c>
       <c r="E60" s="3">
         <v>1094800</v>
@@ -3176,7 +3176,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9200</v>
+        <v>8700</v>
       </c>
       <c r="E62" s="3">
         <v>8800</v>
